--- a/resources/reselling/files/reselling-adv-time-study.xlsx
+++ b/resources/reselling/files/reselling-adv-time-study.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,11 +78,6 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="5">
     <fill>
@@ -133,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -187,8 +182,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -554,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="53" customWidth="1" min="1" max="1"/>
@@ -993,10 +986,6 @@
           <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
         </is>
       </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/reselling/files/reselling-adv-time-study.xlsx
+++ b/resources/reselling/files/reselling-adv-time-study.xlsx
@@ -128,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -178,9 +178,6 @@
     <xf numFmtId="20" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,7 +547,7 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="53" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -560,8 +557,8 @@
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Net per direct hour, by row — scaled to a month (Reselling — Advanced, ch2)</t>
         </is>
@@ -581,8 +578,7 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5" ht="63" customHeight="1">
+    <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Row</t>
@@ -624,7 +620,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="33" customHeight="1">
+    <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>eBay, items selling $25+</t>
@@ -656,7 +652,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1">
+    <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>eBay, items selling under $25</t>
@@ -688,7 +684,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="33" customHeight="1">
+    <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Mercari</t>
@@ -720,7 +716,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="33" customHeight="1">
+    <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Flea market</t>
@@ -752,7 +748,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="33" customHeight="1">
+    <row r="10">
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="6">
         <f>IF(A10="","",SUMIFS('Week log'!$F$6:$F$205,'Week log'!$E$6:$E$205,A10))</f>
@@ -774,7 +770,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="33" customHeight="1">
+    <row r="11">
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="6">
         <f>IF(A11="","",SUMIFS('Week log'!$F$6:$F$205,'Week log'!$E$6:$E$205,A11))</f>
@@ -796,7 +792,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="33" customHeight="1">
+    <row r="12">
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="6">
         <f>IF(A12="","",SUMIFS('Week log'!$F$6:$F$205,'Week log'!$E$6:$E$205,A12))</f>
@@ -818,7 +814,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="33" customHeight="1">
+    <row r="13">
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="6">
         <f>IF(A13="","",SUMIFS('Week log'!$F$6:$F$205,'Week log'!$E$6:$E$205,A13))</f>
@@ -840,7 +836,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="33" customHeight="1">
+    <row r="14">
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="6">
         <f>IF(A14="","",SUMIFS('Week log'!$F$6:$F$205,'Week log'!$E$6:$E$205,A14))</f>
@@ -862,7 +858,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1">
+    <row r="15">
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="6">
         <f>IF(A15="","",SUMIFS('Week log'!$F$6:$F$205,'Week log'!$E$6:$E$205,A15))</f>
@@ -884,7 +880,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="33" customHeight="1">
+    <row r="16">
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="6">
         <f>IF(A16="","",SUMIFS('Week log'!$F$6:$F$205,'Week log'!$E$6:$E$205,A16))</f>
@@ -906,7 +902,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="33" customHeight="1">
+    <row r="17">
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="6">
         <f>IF(A17="","",SUMIFS('Week log'!$F$6:$F$205,'Week log'!$E$6:$E$205,A17))</f>
@@ -964,7 +960,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
@@ -979,11 +974,10 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
+          <t>ePORTS — your ecom source (eports.global)  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
         </is>
       </c>
     </row>
@@ -1009,8 +1003,8 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="123" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Time study — one ordinary week, every block (Reselling — Advanced, ch2)</t>
         </is>
@@ -1030,7 +1024,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -3263,11 +3256,10 @@
         <v/>
       </c>
     </row>
-    <row r="206"/>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
+          <t>ePORTS — your ecom source (eports.global)  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
         </is>
       </c>
     </row>
